--- a/output/full_scan/batch_seq1_2026-10-01.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-01.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>875.0569685954665</v>
+        <v>1015.056968595466</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>66.8</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>58.85925607134453</v>
+        <v>58.85925613638764</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23.9383473578656</v>
+        <v>23.93834744459023</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0.7054909582112754</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0230418380974555</v>
+        <v>0.0230418379528032</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>873.3154130759525</v>
+        <v>1008.315413075953</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>12.4</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.54145356268216</v>
+        <v>59.54145365591146</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.0447272157061</v>
+        <v>25.04472732948552</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1.818980746131936</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.018223430528631</v>
+        <v>0.0182234304997032</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1101</v>
+        <v>1303</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>762.3182738519463</v>
+        <v>968.3809813471432</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25.55</v>
+        <v>254</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.87486503685224</v>
+        <v>63.85587318371346</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>36.98934788325544</v>
+        <v>27.66210518706448</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.535754378370869</v>
+        <v>0.7862400290546225</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1571043270661553</v>
+        <v>0.5031173972649867</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>681.4445132966445</v>
+        <v>896.3322040762221</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>112.5</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>70.61924897700584</v>
+        <v>76.82047824271427</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45.0300185285757</v>
+        <v>39.23043705053792</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.473602630854957</v>
+        <v>0.7332204076222116</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.0366618739219002</v>
+        <v>18.71351682609409</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1560</v>
+        <v>1101</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>646.3322040762221</v>
+        <v>892.3182738519463</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1000</v>
+        <v>25.55</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>76.82047823272318</v>
+        <v>57.87486506097071</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>39.23043704037768</v>
+        <v>36.98934788325544</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.7332204076222116</v>
+        <v>1.535754378370869</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>18.71351682642809</v>
+        <v>0.1571043270772816</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1416</v>
+        <v>1459</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>639.3019482961215</v>
+        <v>826.3152573846605</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11.65</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.02900621622947</v>
+        <v>79.51633265038107</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>13.66140877038656</v>
+        <v>52.35668994240232</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.00843622094015</v>
+        <v>1.475393540195875</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.009761554727771</v>
+        <v>0.0459484973056971</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1459</v>
+        <v>1338</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>636.3152573846606</v>
+        <v>774.3857164073846</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>79.51633261275637</v>
+        <v>61.59828489163919</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>52.35668960059923</v>
+        <v>35.18507569998307</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.475393540195875</v>
+        <v>2.180172545731115</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0459484973819775</v>
+        <v>0.146159912616957</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1338</v>
+        <v>1416</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>634.3857164073847</v>
+        <v>754.3019482961215</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>15.3</v>
+        <v>11.65</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.59828474973123</v>
+        <v>58.02900628895113</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>35.18507567564818</v>
+        <v>13.66140879330637</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.180172545731115</v>
+        <v>2.00843622094015</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.146159912594701</v>
+        <v>0.0097615547055162</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>622.4131401887685</v>
+        <v>738.7873631304562</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>63.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>73.17613482897332</v>
+        <v>61.74331801489512</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>57.40338943441793</v>
+        <v>36.1752537801669</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.041314018876852</v>
+        <v>0.2331378152793961</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.023660652991317</v>
+        <v>-0.2722316583106741</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1528</v>
+        <v>1456</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>602.4991285603558</v>
+        <v>688.0826294840818</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25</v>
+        <v>14.8</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.30054997059586</v>
+        <v>59.52833708839947</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>39.7007347077472</v>
+        <v>19.20817334880186</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.3113105238450177</v>
+        <v>0.7698738283062083</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.147195993786914</v>
+        <v>0.0676895508030235</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1563</v>
+        <v>1102</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>598.7873631304562</v>
+        <v>687.273558802679</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>76.09999999999999</v>
+        <v>35.65</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.74331806097568</v>
+        <v>57.78287131313513</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.17525385449854</v>
+        <v>25.64436066360676</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.2331378152793961</v>
+        <v>1.591640672190632</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.2722316583106741</v>
+        <v>-0.0090625801309131</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1303</v>
+        <v>1558</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>598.3809813471429</v>
+        <v>681.4445132966445</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>254</v>
+        <v>112.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.85587316249627</v>
+        <v>70.61924889274438</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>27.66210511818801</v>
+        <v>45.03001855184005</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7862400290546225</v>
+        <v>2.473602630854957</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.50311739734288</v>
+        <v>-0.0366618737216195</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1315</v>
+        <v>1418</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>585.8401561898506</v>
+        <v>664.3509171322196</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>68.7</v>
+        <v>18.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>71.00772541693279</v>
+        <v>63.64024867535892</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>40.0137549359021</v>
+        <v>25.13708208988477</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2638338555809174</v>
+        <v>0.3710171038279836</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1320365038125114</v>
+        <v>0.117144108863592</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1456</v>
+        <v>1314</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>548.0826294840818</v>
+        <v>656.1900710676859</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14.8</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>59.52833711188394</v>
+        <v>59.21109708551</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>19.20817346823817</v>
+        <v>43.14372196762495</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7698738283062083</v>
+        <v>0.7465361181177446</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.06768955079189801</v>
+        <v>0.0375839722827832</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1314</v>
+        <v>1569</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>541.1900710676861</v>
+        <v>622.4131401887685</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.21109707444057</v>
+        <v>73.17613473742412</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>43.14372198609764</v>
+        <v>57.40338953816346</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7465361181177446</v>
+        <v>1.041314018876852</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0375839722783314</v>
+        <v>1.023660653569935</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1312</v>
+        <v>1528</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>528.387585423886</v>
+        <v>617.4991285603558</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14.6</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.68906996415237</v>
+        <v>61.30054996564407</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>40.89015199205424</v>
+        <v>39.70073472444398</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4329480088550536</v>
+        <v>0.3113105238450177</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.07589777597157039</v>
+        <v>0.1471959937646592</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1539</v>
+        <v>1310</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>526.016554086935</v>
+        <v>612.2932663108198</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>15.65</v>
+        <v>9.02</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>50.1501208297068</v>
+        <v>56.20739525195927</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.3184277570172</v>
+        <v>32.36119073741852</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.213445578840528</v>
+        <v>0.8265056831031046</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0080711059394425</v>
+        <v>0.0410327357975381</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1339</v>
+        <v>1315</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>519.4569064866082</v>
+        <v>605.8401561898506</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.7</v>
+        <v>68.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>44.14798713227894</v>
+        <v>71.0077254910976</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.31339097403206</v>
+        <v>40.01375494476877</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8523139859093252</v>
+        <v>0.2638338555809174</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0133039448400451</v>
+        <v>0.1320365037902711</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1513</v>
+        <v>1568</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>515.580471508547</v>
+        <v>605.2745574256003</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>166.5</v>
+        <v>32.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>52.44686992056043</v>
+        <v>66.96120161348674</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>10.78848093941121</v>
+        <v>25.99985870597757</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8512337835962264</v>
+        <v>1.209871320779198</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1913784777832494</v>
+        <v>0.3777834619196442</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1323</v>
+        <v>1516</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>495.6560073735254</v>
+        <v>587.0676904140998</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>21.5</v>
+        <v>13.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.16399164104736</v>
+        <v>46.7642834361791</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.63056461840714</v>
+        <v>14.4300250070245</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.2188062628698008</v>
+        <v>0.1692273286154572</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.025462947341009</v>
+        <v>0.0125075571672864</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1102</v>
+        <v>1513</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>492.2735588026789</v>
+        <v>580.580471508547</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>35.65</v>
+        <v>166.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.78287146873781</v>
+        <v>52.44687003458705</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.644360648917</v>
+        <v>10.78848101125</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.591640672190632</v>
+        <v>0.8512337835962264</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.009062580108653901</v>
+        <v>0.1913784772269256</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1310</v>
+        <v>1441</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>472.2932663108198</v>
+        <v>568.2501631984111</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9.02</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.2073951365497</v>
+        <v>67.81904284141254</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>32.36119071239342</v>
+        <v>22.24985912084724</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8265056831031046</v>
+        <v>1.013306038894575</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0410327358153421</v>
+        <v>0.1457760853083836</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1516</v>
+        <v>1326</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>472.0676904140998</v>
+        <v>565.3389196197254</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>13.5</v>
+        <v>67.7</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46.76428341574844</v>
+        <v>52.36704541872983</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14.4300250070245</v>
+        <v>27.71924103052504</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.1692273286154572</v>
+        <v>0.6188774846703499</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0125075571895413</v>
+        <v>-0.3342711934549727</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1326</v>
+        <v>1468</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>450.3389196197254</v>
+        <v>565.016418586416</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>67.7</v>
+        <v>13.55</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.3670453781535</v>
+        <v>58.85933002864032</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.71924099892389</v>
+        <v>10.5273369443474</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6188774846703499</v>
+        <v>1.010140690150567</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.3342711934549727</v>
+        <v>0.0401194623712207</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1521</v>
+        <v>1439</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>449.6991305498327</v>
+        <v>563.5840715173375</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>25.8</v>
+        <v>28.95</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.80544373476172</v>
+        <v>53.26889558266873</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.40845974211604</v>
+        <v>17.44063815648874</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.1372254645084575</v>
+        <v>2.415331646273978</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0735988353699749</v>
+        <v>-0.0521543801857904</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1341</v>
+        <v>1307</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>448.8737103160994</v>
+        <v>553.2490851193372</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>59</v>
+        <v>31.45</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.82437209380885</v>
+        <v>61.18915976727674</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.48267328813862</v>
+        <v>14.06335966137276</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9546255600144384</v>
+        <v>1.17056532337911</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4399611930742153</v>
+        <v>0.142918930609804</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1439</v>
+        <v>1321</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>448.5840715173376</v>
+        <v>542.2646109806701</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>28.95</v>
+        <v>32.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>53.26889575317537</v>
+        <v>51.9014933409145</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17.440638158301</v>
+        <v>8.566180558862383</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.415331646273978</v>
+        <v>0.6171226860470618</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.0521543802748086</v>
+        <v>-0.0163490827350013</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1321</v>
+        <v>1539</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>447.2646109806701</v>
+        <v>526.016554086935</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>32.5</v>
+        <v>15.65</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.90149354168501</v>
+        <v>50.15012043326714</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8.566180537390633</v>
+        <v>20.31842770731628</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6171226860470618</v>
+        <v>1.213445578840528</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0163490827461358</v>
+        <v>0.0080711059394425</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1437</v>
+        <v>1339</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>440.8433260193178</v>
+        <v>519.4569064866082</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>31.85</v>
+        <v>42.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46.1312501836026</v>
+        <v>44.14798707059437</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14.17548028364986</v>
+        <v>23.31339099576942</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5588999723087635</v>
+        <v>0.8523139859093252</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1067306845404361</v>
+        <v>0.0133039448845516</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1307</v>
+        <v>1312</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>438.2490851193372</v>
+        <v>518.387585423886</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>31.45</v>
+        <v>14.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>61.18915948364305</v>
+        <v>54.68907002294939</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.06335955006488</v>
+        <v>40.89015202590724</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.17056532337911</v>
+        <v>0.4329480088550536</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.142918930954745</v>
+        <v>-0.07589777600495</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1568</v>
+        <v>1472</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>435.2745574256002</v>
+        <v>500.528541836335</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>32.7</v>
+        <v>88.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>66.96120163480516</v>
+        <v>53.05053683855513</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>25.99985867874062</v>
+        <v>8.576550776621465</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.209871320779198</v>
+        <v>2.534102433765768</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3777834619307689</v>
+        <v>2.148230629542003</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1233</v>
+        <v>1323</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>420.3562552196729</v>
+        <v>495.6560073735254</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>28.1</v>
+        <v>21.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.59775009019823</v>
+        <v>56.1639916863692</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13.30165270025652</v>
+        <v>14.63056461840714</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2913559448009316</v>
+        <v>0.2188062628698008</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0047793892689619</v>
+        <v>-0.0254629473521345</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1434</v>
+        <v>1304</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>412.7572635094959</v>
+        <v>486.0010965547801</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>17.95</v>
+        <v>12.45</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.1927595547509</v>
+        <v>51.84445882509566</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.40486415324857</v>
+        <v>24.18694089107488</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9579653877531344</v>
+        <v>0.6025313152106472</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0169823547714457</v>
+        <v>0.0151349375742305</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1474</v>
+        <v>1521</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>408.9718250283393</v>
+        <v>469.6991305498327</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>10.05</v>
+        <v>25.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.96089237535433</v>
+        <v>54.80543758821073</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24.06743067619849</v>
+        <v>28.40845980139993</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.017431918596361</v>
+        <v>0.1372254645084575</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0195038801615184</v>
+        <v>0.07359883535884849</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1468</v>
+        <v>1527</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>405.016418586416</v>
+        <v>468.7957303463055</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>13.55</v>
+        <v>32.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.85932995814056</v>
+        <v>55.77492860122394</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10.52733704484289</v>
+        <v>11.48117186244279</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.010140690150567</v>
+        <v>1.080906523113256</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0401194623823477</v>
+        <v>0.055131381510877</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1446</v>
+        <v>1341</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>393.6911783202587</v>
+        <v>448.8737103160996</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>13.45</v>
+        <v>59</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.92702217858873</v>
+        <v>51.82437210388535</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.97305515439331</v>
+        <v>10.48267307677988</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2409501876527723</v>
+        <v>0.9546255600144384</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0225643784311283</v>
+        <v>0.4399611924733495</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1213</v>
+        <v>1538</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>387.1782236064402</v>
+        <v>447.8289130764474</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>7</v>
+        <v>7.83</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.38553896880323</v>
+        <v>57.33106809849784</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9.57971714030012</v>
+        <v>11.64600197274603</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.50161724730771</v>
+        <v>1.812561536876331</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0387254380808828</v>
+        <v>0.4727369510681289</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1308</v>
+        <v>1437</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>386.9761744741277</v>
+        <v>440.8433260193178</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>14.2</v>
+        <v>31.85</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.10140074931797</v>
+        <v>46.131250077731</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>29.60583058968682</v>
+        <v>14.17548032629326</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5594837448671419</v>
+        <v>0.5588999723087635</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0158302641943456</v>
+        <v>-0.1067306844959266</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1418</v>
+        <v>1474</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>384.3509171322195</v>
+        <v>428.9718250283393</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>18.5</v>
+        <v>10.05</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>63.64024882345535</v>
+        <v>52.96089224909452</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.13708218334052</v>
+        <v>24.06743068933313</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3710171038279836</v>
+        <v>1.017431918596361</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1171441085186483</v>
+        <v>0.0195038801615184</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1342</v>
+        <v>1319</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>380.176099910775</v>
+        <v>426.5190963163447</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>100</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,49 +2619,49 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>42.06975520145343</v>
+        <v>45.38376909152818</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.94712919909125</v>
+        <v>16.10798459162077</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8663970325883674</v>
+        <v>1.155198897240423</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0774093286774266</v>
+        <v>-0.2466318610049172</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1309</v>
+        <v>1340</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>373.5447573381799</v>
+        <v>425.0336105159557</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>13.7</v>
+        <v>5.23</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.08165409708025</v>
+        <v>52.29390990672725</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.46575269531564</v>
+        <v>13.72896684173844</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5211910259399647</v>
+        <v>0.6496132920346261</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0120431868663442</v>
+        <v>0.0072497114088194</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1304</v>
+        <v>1233</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>371.0010965547796</v>
+        <v>420.3562552196729</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>12.45</v>
+        <v>28.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.84445879644804</v>
+        <v>49.59775000909693</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>24.18694086217616</v>
+        <v>13.30165271227011</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6025313152106472</v>
+        <v>0.2913559448009316</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0151349375964841</v>
+        <v>0.0047793892689619</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1441</v>
+        <v>1218</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>368.2501631984109</v>
+        <v>415.8056452514757</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>67.81904280670071</v>
+        <v>49.77364715259783</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.24985912084724</v>
+        <v>5.267407799416656</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.013306038894575</v>
+        <v>0.4991177482391358</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1457760853260403</v>
+        <v>0.042448985553336</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1527</v>
+        <v>1434</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>358.7957303463055</v>
+        <v>412.7572635094959</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>32.8</v>
+        <v>17.95</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>55.7749294168421</v>
+        <v>51.1927595547509</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>11.48117185523019</v>
+        <v>23.404864175332</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.080906523113256</v>
+        <v>0.9579653877531344</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0551313815553837</v>
+        <v>0.0169823547491874</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1465</v>
+        <v>1446</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>358.5951236016715</v>
+        <v>393.6911783202587</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11.65</v>
+        <v>13.45</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>41.27246790041284</v>
+        <v>43.92702206321866</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.49179634780712</v>
+        <v>21.97305515918375</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3092900882518103</v>
+        <v>0.2409501876527723</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0049188277988426</v>
+        <v>0.0225643783754919</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1103</v>
+        <v>1477</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>357.295637685756</v>
+        <v>390.3085822497445</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>13.2</v>
+        <v>190.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.28459732986701</v>
+        <v>38.38505788239506</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.79484671833834</v>
+        <v>29.04908146273448</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8479476144700043</v>
+        <v>0.7624405066122011</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0093774289743607</v>
+        <v>0.4223887025669288</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>353.4449458938636</v>
+        <v>388.3345371935938</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>24.4</v>
+        <v>274.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.76796512006094</v>
+        <v>28.04663460133629</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9.277524986098957</v>
+        <v>43.35189991073793</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3698190660219487</v>
+        <v>0.6573433371613019</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0395921503435345</v>
+        <v>-0.1389854912958021</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1541</v>
+        <v>1213</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>352.2446203787959</v>
+        <v>387.1782236064402</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>20.75</v>
+        <v>7</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.36293930834671</v>
+        <v>50.38553896613656</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.69641883133526</v>
+        <v>9.579717134442587</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7107586667194579</v>
+        <v>0.50161724730771</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2181163591854389</v>
+        <v>0.0387254381253919</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1414</v>
+        <v>1308</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>347.0507785305819</v>
+        <v>386.9761744741277</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>17.35</v>
+        <v>14.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>39.95428384636133</v>
+        <v>51.10140077503208</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>28.18287268874405</v>
+        <v>29.6058306052089</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4004626955542992</v>
+        <v>0.5594837448671419</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0523011155490684</v>
+        <v>-0.0158302642277278</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3124,21 +3124,21 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1442</v>
+        <v>1417</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>345.1651145372163</v>
+        <v>385.1365171098125</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>26.5</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>28.69794498301953</v>
+        <v>47.85393826472183</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>25.5034678468588</v>
+        <v>25.71419701568254</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.949240152586377</v>
+        <v>1.022308240312889</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.4704801150504194</v>
+        <v>0.0154086704230098</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1475</v>
+        <v>1342</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>337.6320153893299</v>
+        <v>380.176099910775</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>26.05</v>
+        <v>100</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>47.13192517160748</v>
+        <v>42.06975533483251</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.65951419656658</v>
+        <v>18.94712931678946</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3087579183541144</v>
+        <v>0.8663970325883674</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0060154440150028</v>
+        <v>0.0774093286329197</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1402</v>
+        <v>1103</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>337.3260680564677</v>
+        <v>377.2956376857561</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>27.95</v>
+        <v>13.2</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.42522987284704</v>
+        <v>52.28459729206504</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>11.40084618150827</v>
+        <v>22.79484667068169</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.733643051372909</v>
+        <v>0.8479476144700043</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0448583054774174</v>
+        <v>0.009377428963233</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1506</v>
+        <v>1309</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>334.2911506628777</v>
+        <v>373.5447573381797</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>9.5</v>
+        <v>13.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>23.5959455346342</v>
+        <v>50.08165408371541</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>33.86789240249258</v>
+        <v>28.46575268326111</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.761442125788572</v>
+        <v>0.5211910259399647</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0217291600231645</v>
+        <v>-0.0120431868440898</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1319</v>
+        <v>1203</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>331.5190963163447</v>
+        <v>362.4527679806411</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>43.9</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.38376923061774</v>
+        <v>48.55801661507427</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.10798464422266</v>
+        <v>11.80564309956838</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.155198897240423</v>
+        <v>0.1820771343087831</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.2466318610049172</v>
+        <v>0.0447693914233204</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1464</v>
+        <v>1455</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>324.7821293093451</v>
+        <v>358.8546216001343</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10</v>
+        <v>9.84</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.63739158730321</v>
+        <v>51.71367870363301</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>24.06025032266556</v>
+        <v>24.53744336405721</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.038438131790139</v>
+        <v>0.4148070236219652</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0132358397591563</v>
+        <v>-0.0102918045107251</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>323.4230175397201</v>
+        <v>358.5951236016715</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>7.94</v>
+        <v>11.65</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>38.58435458681197</v>
+        <v>41.2724680598136</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10.90237980962091</v>
+        <v>20.49179632992749</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.485403735107803</v>
+        <v>0.3092900882518103</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0214463449926552</v>
+        <v>0.0049188277654619</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1210</v>
+        <v>1402</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>317.1186254390182</v>
+        <v>357.3260680564676</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>51.7</v>
+        <v>27.95</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>42.51535892181422</v>
+        <v>47.42522971191912</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.82763885744405</v>
+        <v>11.40084622390918</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9769257352061304</v>
+        <v>1.733643051372909</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0653660445224043</v>
+        <v>-0.0448583055108035</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1340</v>
+        <v>1470</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>315.0336105159557</v>
+        <v>353.4449458938636</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>5.23</v>
+        <v>24.4</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.29390999630339</v>
+        <v>52.76796419324619</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.72896686342944</v>
+        <v>9.277524999768268</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6496132920346261</v>
+        <v>0.3698190660219487</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0072497114132696</v>
+        <v>0.0395921502767731</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1473</v>
+        <v>1541</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>314.3999840587514</v>
+        <v>352.2446203787959</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>19.25</v>
+        <v>20.75</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>28.43006634587801</v>
+        <v>51.36293930630484</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.39991349163012</v>
+        <v>20.69641898116942</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.636373073814422</v>
+        <v>0.7107586667194579</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0565202964752387</v>
+        <v>0.2181163591520571</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1451</v>
+        <v>1414</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>312.3837747554963</v>
+        <v>347.0507785305819</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>17</v>
+        <v>17.35</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>40.6355425286748</v>
+        <v>39.95428338315296</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.55929545398746</v>
+        <v>28.18287280195283</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.518870553091852</v>
+        <v>0.4004626955542992</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0063709624271015</v>
+        <v>0.0523011156253475</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1218</v>
+        <v>1447</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>305.8056452514757</v>
+        <v>346.6922585930232</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>14.5</v>
+        <v>6.51</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.77364718994379</v>
+        <v>45.61425269788829</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5.267407732550057</v>
+        <v>13.83423022934739</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4991177482391358</v>
+        <v>1.00669654804431</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.042448985531084</v>
+        <v>0.0306369530226056</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1471</v>
+        <v>1442</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>300.4042592218381</v>
+        <v>345.1651145372174</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>9.49</v>
+        <v>26.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.34774090553877</v>
+        <v>28.69794491227769</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.07080911013085</v>
+        <v>25.50346784785964</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4754661684946755</v>
+        <v>1.949240152586377</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0038536839556797</v>
+        <v>-0.4704801150504194</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1227</v>
+        <v>1409</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>299.5718625455879</v>
+        <v>344.4266161914521</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>28.1</v>
+        <v>24.4</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.16582778588206</v>
+        <v>49.30340499204483</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13.17266208642069</v>
+        <v>12.89144938724184</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5570119571424839</v>
+        <v>0.5021814005217331</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0036843536947483</v>
+        <v>-0.0198872750608657</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1529</v>
+        <v>1475</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>295.3401149447682</v>
+        <v>337.6320153893299</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>15.65</v>
+        <v>26.05</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.44308228085158</v>
+        <v>47.13192507768863</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>26.91311152230858</v>
+        <v>20.65951413330704</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4885575027768393</v>
+        <v>0.3087579183541144</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.09566050409581139</v>
+        <v>0.0060154439593675</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1463</v>
+        <v>1506</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>290.0982242167379</v>
+        <v>334.2911506628776</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>17.5</v>
+        <v>9.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>49.58926923389125</v>
+        <v>23.5959455346342</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.02310231657508</v>
+        <v>33.86789237449687</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.162981121499745</v>
+        <v>1.761442125788572</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0235485109679155</v>
+        <v>-0.0217291600231645</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1413</v>
+        <v>1216</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>286.9988624141861</v>
+        <v>333.0222933410764</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>9.25</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.10079141364984</v>
+        <v>40.58773686579256</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.463306465542752</v>
+        <v>10.04820431814053</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4540532121746029</v>
+        <v>0.7320284683350698</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0009572200391219</v>
+        <v>-0.1011910894495689</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1109</v>
+        <v>1533</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>284.9649652942597</v>
+        <v>331.6152410766566</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>13.3</v>
+        <v>30.55</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>36.97385619682262</v>
+        <v>43.9463845187906</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>37.06923501956459</v>
+        <v>15.55310922968344</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.550019080603284</v>
+        <v>0.6772459966981655</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0033739634707927</v>
+        <v>0.077179191188463</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1472</v>
+        <v>1464</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>275.528541836335</v>
+        <v>324.7821293093449</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>88.8</v>
+        <v>10</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.05053684779763</v>
+        <v>44.63739144324644</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8.576550790358299</v>
+        <v>24.06025028721231</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.534102433765768</v>
+        <v>1.038438131790139</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2.148230629074655</v>
+        <v>0.0132358397480306</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1477</v>
+        <v>1467</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>275.3085822497445</v>
+        <v>323.4230175397201</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>190.5</v>
+        <v>7.94</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>38.38505784748247</v>
+        <v>38.58435452402654</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.04908147083324</v>
+        <v>10.90237992694529</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7624405066122011</v>
+        <v>2.485403735107803</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.4223887030120412</v>
+        <v>0.0214463449904297</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1476</v>
+        <v>1210</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>273.3345371935938</v>
+        <v>317.1186254390182</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>274.5</v>
+        <v>51.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,25 +4209,25 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>28.04663467498109</v>
+        <v>42.51535919238246</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>43.35189984610712</v>
+        <v>23.82763910847504</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6573433371613019</v>
+        <v>0.9769257352061304</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1389854912958021</v>
+        <v>0.0653660436322345</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1531</v>
+        <v>1473</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>272.641338271715</v>
+        <v>314.3999840587563</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>11.6</v>
+        <v>19.25</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>36.14324424207334</v>
+        <v>28.43006619154534</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.60779297773668</v>
+        <v>32.39991315445417</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.42728719545863</v>
+        <v>1.636373073814422</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0292935963864361</v>
+        <v>-0.0565202965308815</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1236</v>
+        <v>1451</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>260.4030049868829</v>
+        <v>312.3837747554963</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>25.5</v>
+        <v>17</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.61593868315286</v>
+        <v>40.63554194708598</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.87719624022277</v>
+        <v>20.55929549982849</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2712925680240223</v>
+        <v>2.518870553091852</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.07060337077291221</v>
+        <v>-0.0063709624382268</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1216</v>
+        <v>1471</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>257.8326471633932</v>
+        <v>300.4042592218382</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,49 +4368,49 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>40.58773682275985</v>
+        <v>47.34774066849951</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.04820424327049</v>
+        <v>13.07080911013084</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7052505837229839</v>
+        <v>0.4754661684946755</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.1011910892492758</v>
+        <v>0.0038536839668076</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>257.7750021946904</v>
+        <v>299.5718625455876</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>105.5</v>
+        <v>28.1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.96919129414152</v>
+        <v>41.1658277184316</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.9014934293101</v>
+        <v>13.1726619966266</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4753614034673482</v>
+        <v>0.5570119571424839</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.2887649596733707</v>
+        <v>0.0036843536168593</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>256.4166250082988</v>
+        <v>297.9305105727113</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>24.2</v>
+        <v>79.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.12396744585166</v>
+        <v>43.4420221439664</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.78013336908553</v>
+        <v>10.29588868548135</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7782561427506864</v>
+        <v>0.966728644229792</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0047762946358641</v>
+        <v>0.1196290016630898</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1232</v>
+        <v>1529</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>252.8733613068512</v>
+        <v>295.3401149447682</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>153</v>
+        <v>15.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>40.09069983797707</v>
+        <v>43.44308245010493</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.70808002501303</v>
+        <v>26.91311152230858</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.219286541965137</v>
+        <v>0.4885575027768393</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.286895044315679</v>
+        <v>0.09566050411806459</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1324</v>
+        <v>1463</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>251.2074887432222</v>
+        <v>290.098224216738</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10.05</v>
+        <v>17.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.54423691983965</v>
+        <v>49.58926921038706</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.13717430361706</v>
+        <v>17.02310233901725</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.173807186192958</v>
+        <v>0.162981121499745</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0053509574041434</v>
+        <v>0.0235485109456638</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1537</v>
+        <v>1413</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>251.1210334223334</v>
+        <v>286.9988624141861</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>115</v>
+        <v>9.25</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.86924636901755</v>
+        <v>49.10079155076688</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>34.31633426070626</v>
+        <v>9.463306424699738</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.354782579992597</v>
+        <v>0.4540532121746029</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.3329643209437178</v>
+        <v>0.00095722001687</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1460</v>
+        <v>1109</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>250.350895285255</v>
+        <v>284.9649652942598</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>6.23</v>
+        <v>13.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>31.95969369182345</v>
+        <v>36.97385653965395</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>22.7849791893636</v>
+        <v>37.06923487139419</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.775893836452814</v>
+        <v>1.550019080603284</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.00568728934747</v>
+        <v>0.0033739634485388</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1417</v>
+        <v>1526</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>250.1365171098125</v>
+        <v>277.4882219539903</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>14.95</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.85393832829963</v>
+        <v>42.88868775554516</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25.71419696315189</v>
+        <v>22.11287042338728</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.022308240312889</v>
+        <v>0.2514958412590212</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0154086704163336</v>
+        <v>0.0472306078190857</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1538</v>
+        <v>1225</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>247.8289130764474</v>
+        <v>276.4166250082988</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>7.83</v>
+        <v>24.2</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>57.33106683760056</v>
+        <v>41.12396738662188</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.6460010502797</v>
+        <v>21.78013342436022</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.812561536876331</v>
+        <v>0.7782561427506864</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.4727369571657984</v>
+        <v>-0.004776294591355</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1455</v>
+        <v>1531</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>243.8546216001343</v>
+        <v>272.641338271715</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>9.84</v>
+        <v>11.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>51.71367873414773</v>
+        <v>36.14324422299634</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>24.53744335572049</v>
+        <v>18.60779295431772</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4148070236219652</v>
+        <v>0.42728719545863</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0102918045084995</v>
+        <v>0.0292935963864361</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1316</v>
+        <v>1236</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>241.3979639300217</v>
+        <v>260.4030049868829</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.3136383335728</v>
+        <v>48.61593886268067</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.4447810419172</v>
+        <v>15.87719651584354</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7061056144940847</v>
+        <v>0.2712925680240223</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0365334708009523</v>
+        <v>-0.0706033708174174</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1201</v>
+        <v>1503</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>238.8677839966905</v>
+        <v>258.6615605223581</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>11.6</v>
+        <v>197.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,49 +4951,49 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>36.41398943883326</v>
+        <v>46.51947516486819</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>37.31044719687058</v>
+        <v>9.486432739730985</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.571301032095653</v>
+        <v>0.3093397493561166</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0329108512436606</v>
+        <v>-0.2243066722961386</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1454</v>
+        <v>1215</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>237.1503966852813</v>
+        <v>257.7750021946906</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>12.15</v>
+        <v>105.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.88459072633076</v>
+        <v>41.969191452402</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21.08809285355172</v>
+        <v>13.90149343664659</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3542101156920424</v>
+        <v>0.4753614034673482</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.029902985538406</v>
+        <v>-0.2887649597846399</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1435</v>
+        <v>1454</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>235.5801433137312</v>
+        <v>257.1503966852823</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>22</v>
+        <v>12.15</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.50361436523783</v>
+        <v>40.88459072633076</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7.770555897186414</v>
+        <v>21.08809289831155</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.690966230691641</v>
+        <v>0.3542101156920424</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2943010397463946</v>
+        <v>-0.0299029855495331</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1512</v>
+        <v>1435</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>234.2414693363182</v>
+        <v>255.5801433137312</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.3507081102323</v>
+        <v>50.50361441646702</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8.786598737017561</v>
+        <v>7.770555920022971</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.093060793965352</v>
+        <v>1.690966230691641</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0105959708348687</v>
+        <v>0.2943010394173607</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1423</v>
+        <v>1232</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>231.6964936122113</v>
+        <v>252.8733613068512</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>35.5</v>
+        <v>153</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>51.86295589886624</v>
+        <v>40.09069977456801</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.07802487591935</v>
+        <v>12.70808002501304</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2055698170326354</v>
+        <v>1.219286541965137</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.7216656804925876</v>
+        <v>-0.286895044315679</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1447</v>
+        <v>1324</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>231.6922585930232</v>
+        <v>251.2074887432222</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>6.51</v>
+        <v>10.05</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.61425278020693</v>
+        <v>50.54423708607718</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.8342302213773</v>
+        <v>15.13717431014167</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.00669654804431</v>
+        <v>1.173807186192958</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0306369530359574</v>
+        <v>0.0053509573818928</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1409</v>
+        <v>1537</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>229.4266161914521</v>
+        <v>251.1210334223334</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>24.4</v>
+        <v>115</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.30340501692972</v>
+        <v>37.86924640248699</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.89144942048285</v>
+        <v>34.31633426070626</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5021814005217331</v>
+        <v>1.354782579992597</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0198872750608657</v>
+        <v>0.3329643207211865</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1203</v>
+        <v>1460</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>227.452767980641</v>
+        <v>250.350895285255</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>43.9</v>
+        <v>6.23</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.55801655950027</v>
+        <v>31.95969360944075</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.8056430487088</v>
+        <v>22.78497918639206</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.1820771343087831</v>
+        <v>0.775893836452814</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0447693914678291</v>
+        <v>-0.00568728934747</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1514</v>
+        <v>1440</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>224.8655132590312</v>
+        <v>242.2554018100869</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>102</v>
+        <v>13.4</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>49.10567898204314</v>
+        <v>49.33752508103122</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.99555505217222</v>
+        <v>12.10444082576642</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5470237566674349</v>
+        <v>0.9085940530657488</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.2286349035727368</v>
+        <v>-0.0029702694458505</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1524</v>
+        <v>1316</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>224.1927648364868</v>
+        <v>241.3979639300217</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>25.95</v>
+        <v>10.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.0574376494337</v>
+        <v>46.31363825481469</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>29.39374119364215</v>
+        <v>20.44478103368868</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7521336480842564</v>
+        <v>0.7061056144940847</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0110965962934458</v>
+        <v>-0.0365334708454621</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1231</v>
+        <v>1201</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>222.9305105727113</v>
+        <v>238.8677839966906</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>79.8</v>
+        <v>11.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.44202208236398</v>
+        <v>36.41398943883326</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10.2958887927179</v>
+        <v>37.31044707329186</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.966728644229792</v>
+        <v>0.571301032095653</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.11962900288708</v>
+        <v>-0.0329108512770407</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1533</v>
+        <v>1453</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>221.6152410766567</v>
+        <v>237.7489518442059</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>30.55</v>
+        <v>10.9</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.94638462791882</v>
+        <v>44.98214737923286</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15.55310922587048</v>
+        <v>14.52500753688451</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6772459966981655</v>
+        <v>0.3893660840294056</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.07717919111057039</v>
+        <v>-0.0026181359159133</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1453</v>
+        <v>1229</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>217.7489518442059</v>
+        <v>234.5365667523865</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>10.9</v>
+        <v>40.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.9821475061114</v>
+        <v>43.96087765789789</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.52500758827789</v>
+        <v>17.70884802110433</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3893660840294056</v>
+        <v>1.266449874177196</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0026181359270413</v>
+        <v>-0.0792993949235517</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1582</v>
+        <v>1512</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>215.2443056520234</v>
+        <v>234.2414693363182</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.49275354619103</v>
+        <v>43.35070798284903</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.62299406270059</v>
+        <v>8.786598739827864</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7015041309488318</v>
+        <v>1.093060793965352</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1446199800374936</v>
+        <v>0.0105959708482212</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>214.5365667523864</v>
+        <v>231.9723538537138</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>40.2</v>
+        <v>10.85</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>43.96087774886301</v>
+        <v>49.73575983256234</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.70884799512955</v>
+        <v>17.9112635698688</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.266449874177196</v>
+        <v>0.7215828323524256</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0792993949013029</v>
+        <v>0.0194724520702127</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1519</v>
+        <v>1438</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>214.0480425499082</v>
+        <v>231.7634914736031</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>688</v>
+        <v>21.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.5446662770631</v>
+        <v>49.436583983553</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.06856079181207</v>
+        <v>9.77675006353414</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6747505069328043</v>
+        <v>0.4573813452073672</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-3.179631389917956</v>
+        <v>-0.0151437386618603</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1220</v>
+        <v>1423</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>211.9723538537138</v>
+        <v>231.6964936122113</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>10.85</v>
+        <v>35.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.73575996253538</v>
+        <v>51.86295590149226</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.91126355020358</v>
+        <v>10.07802490050309</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7215828323524256</v>
+        <v>0.2055698170326354</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0194724520702127</v>
+        <v>0.7216656803924453</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1438</v>
+        <v>1515</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>211.7634914736031</v>
+        <v>231.0172058414956</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>21.8</v>
+        <v>29.25</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.43658401429168</v>
+        <v>42.20554137985615</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>9.776750042237664</v>
+        <v>7.654689585902983</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4573813452073672</v>
+        <v>0.6735557277126635</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,11 +5870,11 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0151437386618603</v>
+        <v>0.0103164141123446</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>207.6886870781742</v>
+        <v>227.6886870781744</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>14.45</v>
@@ -5908,13 +5908,13 @@
         <v>52.20627262380211</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14.83202777262723</v>
+        <v>14.83202786365881</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.8216123933265995</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0079161445195005</v>
+        <v>-0.007916144530627601</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>200.4199012165473</v>
+        <v>224.865513259031</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>10.4</v>
+        <v>102</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.60553401071623</v>
+        <v>49.10567900510092</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>22.32080291254816</v>
+        <v>13.99555507620704</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6449249815528408</v>
+        <v>0.5470237566674349</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.01167885132963</v>
+        <v>0.2286349034614555</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1443</v>
+        <v>1524</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>191.5498703070209</v>
+        <v>224.1927648364877</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>23.35</v>
+        <v>25.95</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.56099305230615</v>
+        <v>40.05743770168225</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>5.076637441298849</v>
+        <v>29.39374116706912</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2195776003043794</v>
+        <v>0.7521336480842564</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0308395777555064</v>
+        <v>0.0110965961933044</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1504</v>
+        <v>1582</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>191.106008569597</v>
+        <v>215.2443056520234</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.45006804112796</v>
+        <v>46.49275346405287</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>12.95748190551893</v>
+        <v>21.62299405904008</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4419973632026</v>
+        <v>0.7015041309488318</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2076154677418258</v>
+        <v>0.1446199799484815</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1256</v>
+        <v>1519</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>187.2624816611826</v>
+        <v>214.0480425499084</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>168.5</v>
+        <v>688</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.46236245462138</v>
+        <v>41.54466622859331</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>8.05641724789136</v>
+        <v>11.06856073705897</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.23775889894211</v>
+        <v>0.6747505069328043</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0400739486741694</v>
+        <v>-3.179631388360221</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1466</v>
+        <v>1443</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>170.7770207599875</v>
+        <v>211.549870307021</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>14.7</v>
+        <v>23.35</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.21414760049445</v>
+        <v>47.56099310830463</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10.75002619594304</v>
+        <v>5.076637468252796</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5393557130823359</v>
+        <v>0.2195776003043794</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.009978586689055101</v>
+        <v>0.0308395777109969</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1440</v>
+        <v>1504</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>167.2554018100874</v>
+        <v>211.1060085695967</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>13.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,49 +6223,49 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>49.33752505225861</v>
+        <v>46.45006807849737</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.10444082949789</v>
+        <v>12.95748191449393</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9085940530657488</v>
+        <v>0.4419973632026</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0029702694235958</v>
+        <v>-0.2076154678976086</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1108</v>
+        <v>1517</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>166.2479358997779</v>
+        <v>200.4199012165473</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11.15</v>
+        <v>10.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>35.34542407986793</v>
+        <v>39.60553392985267</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>51.03168078838346</v>
+        <v>22.32080294402818</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5380765517997956</v>
+        <v>0.6449249815528408</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0257346727665991</v>
+        <v>0.01167885132963</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>166.0172058414956</v>
+        <v>198.6904914725916</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>29.25</v>
+        <v>63.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.20554141712979</v>
+        <v>50.86207105579197</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7.654689585902983</v>
+        <v>17.90282335342064</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6735557277126635</v>
+        <v>1.148238631885886</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0103164140900879</v>
+        <v>0.5704839907869053</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1445</v>
+        <v>1219</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>164.5400996793297</v>
+        <v>195.6779902832228</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>10</v>
+        <v>11.45</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>40.71788797589866</v>
+        <v>50.61991292732188</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.025014226798</v>
+        <v>16.25774897278842</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.676759588688663</v>
+        <v>0.4281798499635649</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0009221575416847</v>
+        <v>0.0019738222385484</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1432</v>
+        <v>1256</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>163.4056370881805</v>
+        <v>187.2624816611826</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>15.05</v>
+        <v>168.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>52.09733601359497</v>
+        <v>39.46236248403068</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.61854031883024</v>
+        <v>8.05641730182429</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7701088389211715</v>
+        <v>0.23775889894211</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0132742108553278</v>
+        <v>-0.0400739488966581</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1419</v>
+        <v>1108</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>163.1818699560357</v>
+        <v>186.2479358997779</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>65.8</v>
+        <v>11.15</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>47.45922300182722</v>
+        <v>35.34542445682976</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>10.06986605770039</v>
+        <v>51.03168079197172</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3510097065175553</v>
+        <v>0.5380765517997956</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0939095305312543</v>
+        <v>0.0257346727665991</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1110</v>
+        <v>1445</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>162.827721726638</v>
+        <v>184.5400996793296</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>14.65</v>
+        <v>10</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>30.62564208487113</v>
+        <v>40.71788823059051</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>30.42065049689215</v>
+        <v>11.0250143202639</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3950193159521811</v>
+        <v>0.676759588688663</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.1106572694042321</v>
+        <v>-0.0009221575305573</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1526</v>
+        <v>1466</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>162.4882219539903</v>
+        <v>170.7770207599875</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>14.95</v>
+        <v>14.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.88868789748349</v>
+        <v>36.21414751246034</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.11287042742745</v>
+        <v>10.7500261914623</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2514958412590212</v>
+        <v>0.5393557130823359</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0472306078079605</v>
+        <v>0.0099785866779292</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1305</v>
+        <v>1432</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>158.2777256445463</v>
+        <v>163.4056370881805</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>12.15</v>
+        <v>15.05</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>50.84893676663356</v>
+        <v>52.09733594394579</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.35468092828924</v>
+        <v>11.61854017807701</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4529747308710152</v>
+        <v>0.7701088389211715</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0108314261198906</v>
+        <v>0.0132742108664546</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1540</v>
+        <v>1419</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>155.0225388680037</v>
+        <v>163.1818699560323</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>19.5</v>
+        <v>65.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>49.38274794395269</v>
+        <v>47.45922296378218</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.20304060984304</v>
+        <v>10.06986611939069</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4640597288929058</v>
+        <v>0.3510097065175553</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0316238851589908</v>
+        <v>-0.0939095305980196</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1217</v>
+        <v>1110</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>153.8636900010632</v>
+        <v>162.8277217266381</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>14.65</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.68657590309301</v>
+        <v>30.62564204758473</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.73405516888439</v>
+        <v>30.42065042770178</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5721180231287555</v>
+        <v>0.3950193159521811</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0039749300217257</v>
+        <v>-0.1106572693931066</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1410</v>
+        <v>1305</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>151.6796081189973</v>
+        <v>158.2777256445463</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>24.15</v>
+        <v>12.15</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.54900684737222</v>
+        <v>50.84893678345276</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>7.109367943357521</v>
+        <v>14.35468099137622</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2878972662949239</v>
+        <v>0.4529747308710152</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0194918279944026</v>
+        <v>0.0108314260976349</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>146.2318331499645</v>
+        <v>155.0225388680038</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>46.65</v>
+        <v>19.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.45951617792032</v>
+        <v>49.3827476039547</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8.982280802237675</v>
+        <v>13.20304062423324</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.5069997591683612</v>
+        <v>0.4640597288929058</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0651241094832728</v>
+        <v>0.0316238851478632</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1503</v>
+        <v>1217</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>143.6615605223576</v>
+        <v>153.8636900010635</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>197.5</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.51947517565107</v>
+        <v>50.68657609091557</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.486432730059921</v>
+        <v>11.73405521919752</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3093397493561166</v>
+        <v>0.5721180231287555</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.2243066720735931</v>
+        <v>-0.0039749300328529</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1444</v>
+        <v>1410</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>142.6373557203361</v>
+        <v>151.6796081189973</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>6.9</v>
+        <v>24.15</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.25635601505872</v>
+        <v>42.54900697407145</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.45120565502777</v>
+        <v>7.10936799737343</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.802559144494923</v>
+        <v>0.2878972662949239</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0332777437839552</v>
+        <v>0.0194918279053837</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>140.3065675464744</v>
+        <v>146.2318331499645</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>26.85</v>
+        <v>46.65</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>38.11672490478752</v>
+        <v>41.45951636646417</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>21.01234728425792</v>
+        <v>8.98228082524961</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.482154652575057</v>
+        <v>0.5069997591683612</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0449050208355947</v>
+        <v>0.06512410966130509</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1522</v>
+        <v>1444</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>108.9024193755479</v>
+        <v>142.6373557203361</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>26.45</v>
+        <v>6.9</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>45.83048313835653</v>
+        <v>46.25635598127266</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.89188067843878</v>
+        <v>17.45120576611921</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4535373731639378</v>
+        <v>0.802559144494923</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.1577166658401485</v>
+        <v>0.0332777437572494</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1436</v>
+        <v>1530</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>108.5258836002251</v>
+        <v>140.3065675464746</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>35.35</v>
+        <v>26.85</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>36.32824748465659</v>
+        <v>38.11672442284771</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.51504823517616</v>
+        <v>21.01234758590533</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5589190174761955</v>
+        <v>0.482154652575057</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,11 +7142,11 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1100590782414139</v>
+        <v>-0.0449050206019272</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>97.97930195892708</v>
+        <v>117.9793019589271</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>25.7</v>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>48.14818849544313</v>
+        <v>48.14818841765354</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>16.19241561952848</v>
+        <v>16.19241561249337</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.6274812499195965</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0198176588735004</v>
+        <v>0.0198176588623674</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>91.1865508452769</v>
+        <v>111.1865508452769</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>45.85</v>
@@ -7233,13 +7233,13 @@
         <v>52.99544859410157</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>11.93435303782725</v>
+        <v>11.93435306499681</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3943128575303131</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.1270647319144191</v>
+        <v>0.1270647319366706</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1532</v>
+        <v>1522</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>86.57626534143614</v>
+        <v>108.9024193755478</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>22.2</v>
+        <v>26.45</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>41.59765366609472</v>
+        <v>45.83048441690843</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>13.65687320932363</v>
+        <v>18.89188054911638</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.6192424401135622</v>
+        <v>0.4535373731639378</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0569890077393582</v>
+        <v>0.1577166650167419</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1219</v>
+        <v>1436</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>85.6779902832228</v>
+        <v>108.5258836002251</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>11.45</v>
+        <v>35.35</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>50.61991301458197</v>
+        <v>36.3282475507881</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>16.25774892803118</v>
+        <v>18.51504809230901</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.4281798499635649</v>
+        <v>0.5589190174761955</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0019738222385484</v>
+        <v>-0.1100590785529779</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7364,21 +7364,21 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>1104</v>
+        <v>1532</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>77.51061173777794</v>
+        <v>106.5762653414361</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>46.39224757057158</v>
+        <v>41.59765369764921</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>11.33770756956972</v>
+        <v>13.65687323885264</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.9413067041561356</v>
+        <v>0.6192424401135622</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0384947509251588</v>
+        <v>-0.0569890077727385</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>1452</v>
+        <v>1104</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>73.79314671638596</v>
+        <v>77.51061173777794</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>10.8</v>
+        <v>26.7</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>36.53992483548856</v>
+        <v>46.39224753276491</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>19.962104601648</v>
+        <v>11.33770757061117</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.2859861960473501</v>
+        <v>0.9413067041561356</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0148401820832141</v>
+        <v>-0.0384947509140305</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7470,21 +7470,21 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>1525</v>
+        <v>1452</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>-1.309508527409628</v>
+        <v>73.79314671638592</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>63.7</v>
+        <v>10.8</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>50.86207107466328</v>
+        <v>36.53992486530294</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>17.90282335051522</v>
+        <v>19.96210463935783</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.148238631885886</v>
+        <v>0.2859861960473501</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,11 +7513,11 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.5704839906533787</v>
+        <v>-0.0148401820943407</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
